--- a/cyclers/nhr-9200-three-cell-chamber/V0.1/nhr-9200-three-cell-chamber.xlsx
+++ b/cyclers/nhr-9200-three-cell-chamber/V0.1/nhr-9200-three-cell-chamber.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Battery-Lab-Hardware\cyclers\nhr-9200-three-cell-chamber\V0.1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0328DAFA-1F24-4EB1-A7FA-B99DA6E4787E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439EAADE-98E2-4272-B05F-48E6AFF63402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
